--- a/output/graficos_dimensiones/comunal_d_env_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:18</t>
+    <t xml:space="preserve">2026-09-10 01:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:32</t>
+    <t xml:space="preserve">2026-09-12 22:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_valparaiso.xlsx
@@ -63,12 +63,12 @@
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Petorca</t>
   </si>
   <si>
-    <t xml:space="preserve">Santo Domingo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puchuncaví</t>
   </si>
   <si>
@@ -108,12 +108,12 @@
     <t xml:space="preserve">Quintero</t>
   </si>
   <si>
+    <t xml:space="preserve">Casablanca</t>
+  </si>
+  <si>
     <t xml:space="preserve">Panquehue</t>
   </si>
   <si>
-    <t xml:space="preserve">Casablanca</t>
-  </si>
-  <si>
     <t xml:space="preserve">Santa María</t>
   </si>
   <si>
@@ -132,12 +132,12 @@
     <t xml:space="preserve">Rinconada</t>
   </si>
   <si>
+    <t xml:space="preserve">Juan Fernández</t>
+  </si>
+  <si>
     <t xml:space="preserve">Calera</t>
   </si>
   <si>
-    <t xml:space="preserve">Juan Fernández</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calle Larga</t>
   </si>
   <si>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:43</t>
+    <t xml:space="preserve">2026-09-24 00:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -589,7 +589,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>180.02</v>
+        <v>192.67</v>
       </c>
     </row>
     <row r="3">
@@ -606,7 +606,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>177.74</v>
+        <v>190.49</v>
       </c>
     </row>
     <row r="4">
@@ -623,7 +623,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>169.61</v>
+        <v>181.95</v>
       </c>
     </row>
     <row r="5">
@@ -640,7 +640,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>148.76</v>
+        <v>159.51</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +657,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>140.27</v>
+        <v>151.13</v>
       </c>
     </row>
     <row r="7">
@@ -674,7 +674,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>138.14</v>
+        <v>146.11</v>
       </c>
     </row>
     <row r="8">
@@ -691,7 +691,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>135.19</v>
+        <v>144.52</v>
       </c>
     </row>
     <row r="9">
@@ -708,7 +708,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>134.01</v>
+        <v>143.71</v>
       </c>
     </row>
     <row r="10">
@@ -725,7 +725,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>129.5</v>
+        <v>138.69</v>
       </c>
     </row>
     <row r="11">
@@ -742,7 +742,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>128.88</v>
+        <v>138.12</v>
       </c>
     </row>
     <row r="12">
@@ -753,13 +753,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5404</v>
+        <v>5606</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>127.08</v>
+        <v>137.37</v>
       </c>
     </row>
     <row r="13">
@@ -770,13 +770,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>5606</v>
+        <v>5404</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>126.96</v>
+        <v>137.24</v>
       </c>
     </row>
     <row r="14">
@@ -793,7 +793,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>123.13</v>
+        <v>132.73</v>
       </c>
     </row>
     <row r="15">
@@ -810,7 +810,7 @@
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>123.06</v>
+        <v>132.67</v>
       </c>
     </row>
     <row r="16">
@@ -827,7 +827,7 @@
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>122.31</v>
+        <v>132.48</v>
       </c>
     </row>
     <row r="17">
@@ -844,7 +844,7 @@
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>120.74</v>
+        <v>129.13</v>
       </c>
     </row>
     <row r="18">
@@ -861,7 +861,7 @@
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>119.89</v>
+        <v>128.34</v>
       </c>
     </row>
     <row r="19">
@@ -878,7 +878,7 @@
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>119.18</v>
+        <v>128.14</v>
       </c>
     </row>
     <row r="20">
@@ -895,7 +895,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>115.38</v>
+        <v>124.11</v>
       </c>
     </row>
     <row r="21">
@@ -912,7 +912,7 @@
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>115.06</v>
+        <v>123.73</v>
       </c>
     </row>
     <row r="22">
@@ -929,7 +929,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>113.35</v>
+        <v>122.46</v>
       </c>
     </row>
     <row r="23">
@@ -946,7 +946,7 @@
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>112.27</v>
+        <v>120.71</v>
       </c>
     </row>
     <row r="24">
@@ -963,7 +963,7 @@
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>111.47</v>
+        <v>119.04</v>
       </c>
     </row>
     <row r="25">
@@ -980,7 +980,7 @@
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>109.63</v>
+        <v>117.6</v>
       </c>
     </row>
     <row r="26">
@@ -997,7 +997,7 @@
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>109.47</v>
+        <v>117.57</v>
       </c>
     </row>
     <row r="27">
@@ -1008,13 +1008,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>5704</v>
+        <v>5102</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>109.28</v>
+        <v>116.93</v>
       </c>
     </row>
     <row r="28">
@@ -1025,13 +1025,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>5102</v>
+        <v>5704</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>109.26</v>
+        <v>116.69</v>
       </c>
     </row>
     <row r="29">
@@ -1048,7 +1048,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>107.31</v>
+        <v>115.66</v>
       </c>
     </row>
     <row r="30">
@@ -1065,7 +1065,7 @@
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>105.55</v>
+        <v>113.73</v>
       </c>
     </row>
     <row r="31">
@@ -1082,7 +1082,7 @@
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>102.6</v>
+        <v>110.01</v>
       </c>
     </row>
     <row r="32">
@@ -1099,7 +1099,7 @@
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>98.78</v>
+        <v>106.06</v>
       </c>
     </row>
     <row r="33">
@@ -1116,7 +1116,7 @@
         <v>2022</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>87.55</v>
+        <v>93.45</v>
       </c>
     </row>
     <row r="34">
@@ -1133,7 +1133,7 @@
         <v>2022</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>87.27</v>
+        <v>92.65</v>
       </c>
     </row>
     <row r="35">
@@ -1144,13 +1144,13 @@
         <v>38</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>5502</v>
+        <v>5104</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>81.89</v>
+        <v>87.96</v>
       </c>
     </row>
     <row r="36">
@@ -1161,13 +1161,13 @@
         <v>39</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>5104</v>
+        <v>5502</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>81.55</v>
+        <v>86.11</v>
       </c>
     </row>
     <row r="37">
@@ -1184,7 +1184,7 @@
         <v>2022</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>79.63</v>
+        <v>85.19</v>
       </c>
     </row>
     <row r="38">
@@ -1201,7 +1201,7 @@
         <v>2022</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>59.73</v>
+        <v>61.58</v>
       </c>
     </row>
     <row r="39">
@@ -1218,7 +1218,7 @@
         <v>2022</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>54.43</v>
+        <v>58.22</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:12</t>
+    <t xml:space="preserve">2026-10-02 16:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:02</t>
+    <t xml:space="preserve">2026-10-04 10:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:44</t>
+    <t xml:space="preserve">2026-10-05 16:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
